--- a/drivers/xlsx/testdata/actor_header.xlsx
+++ b/drivers/xlsx/testdata/actor_header.xlsx
@@ -40,7 +40,7 @@
     <t>last_update</t>
   </si>
   <si>
-    <t>2020-02-15T06:59:28Z</t>
+    <t>2006-02-15T04:34:33Z</t>
   </si>
   <si>
     <t>first_name</t>
